--- a/processed_ruby_restored_xlsx/sc234_凛６：花火.ss.xlsx
+++ b/processed_ruby_restored_xlsx/sc234_凛６：花火.ss.xlsx
@@ -626,8 +626,8 @@
       </c>
       <c r="B11" s="1" t="inlineStr">
         <is>
-          <t>Speak of the devil… I was thinking about Rin-chan, and
-she showed up.</t>
+          <t>Speak of the devil… I was thinking about Rin-chan,
+and she showed up.</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1145,8 +1145,8 @@
       </c>
       <c r="B45" s="1" t="inlineStr">
         <is>
-          <t>I get it— for Rin that's a perfectly good reason to be
-in despair.</t>
+          <t>I get it— for Rin that's a perfectly good reason to
+be in despair.</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -1434,8 +1434,8 @@
       </c>
       <c r="B64" s="1" t="inlineStr">
         <is>
-          <t>「…You're saying it like it's noble, but the premise is
-totally off, isn't it？」</t>
+          <t>「…You're saying it like it's noble, but the premise
+is totally off, isn't it？」</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -1617,8 +1617,8 @@
       </c>
       <c r="B76" s="1" t="inlineStr">
         <is>
-          <t>「I'll give you a goodnight and good morning kiss every
-day too.」</t>
+          <t>「I'll give you a goodnight and good morning kiss
+every day too.」</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -2106,8 +2106,8 @@
       </c>
       <c r="B108" s="1" t="inlineStr">
         <is>
-          <t>Rin-chan immediately opened the wrapper and stuffed it
-into her mouth.</t>
+          <t>Rin-chan immediately opened the wrapper and stuffed
+it into her mouth.</t>
         </is>
       </c>
       <c r="C108" t="n">
@@ -2991,8 +2991,8 @@
       </c>
       <c r="B166" s="1" t="inlineStr">
         <is>
-          <t>I keep wondering if it's really okay to take advantage
-of this….</t>
+          <t>I keep wondering if it's really okay to take
+advantage of this….</t>
         </is>
       </c>
       <c r="C166" t="n">
@@ -3251,8 +3251,8 @@
       </c>
       <c r="B183" s="1" t="inlineStr">
         <is>
-          <t>Rin-chan, looking satisfied, keeps trailing her tongue
-over my lips in a sticky way.</t>
+          <t>Rin-chan, looking satisfied, keeps trailing her
+tongue over my lips in a sticky way.</t>
         </is>
       </c>
       <c r="C183" t="n">
@@ -3711,8 +3711,8 @@
       </c>
       <c r="B213" s="1" t="inlineStr">
         <is>
-          <t>As if just teasing my teeth wasn't enough anymore, her
-tongue started tangling with mine.</t>
+          <t>As if just teasing my teeth wasn't enough anymore,
+her tongue started tangling with mine.</t>
         </is>
       </c>
       <c r="C213" t="n">
@@ -3833,8 +3833,8 @@
       </c>
       <c r="B221" s="1" t="inlineStr">
         <is>
-          <t>As Rin-chan keeps pouring her saliva in, my whole body
-starts to burn up.</t>
+          <t>As Rin-chan keeps pouring her saliva in, my whole
+body starts to burn up.</t>
         </is>
       </c>
       <c r="C221" t="n">
@@ -3849,8 +3849,8 @@
       </c>
       <c r="B222" s="1" t="inlineStr">
         <is>
-          <t>It feels like pleasure is slowly seeping through every
-part of me….</t>
+          <t>It feels like pleasure is slowly seeping through
+every part of me….</t>
         </is>
       </c>
       <c r="C222" t="n">
@@ -3925,8 +3925,8 @@
       </c>
       <c r="B227" s="1" t="inlineStr">
         <is>
-          <t>After tasting Rin-chan’s saliva and letting it flow to
-the back of my throat, the spot it passes through
+          <t>After tasting Rin-chan’s saliva and letting it flow
+to the back of my throat, the spot it passes through
 heats up all at once.</t>
         </is>
       </c>
@@ -3958,8 +3958,8 @@
       </c>
       <c r="B229" s="1" t="inlineStr">
         <is>
-          <t>The hot liquid surges back and my esophagus feels like
-it’s burning from the intense heat.</t>
+          <t>The hot liquid surges back and my esophagus feels
+like it’s burning from the intense heat.</t>
         </is>
       </c>
       <c r="C229" t="n">
@@ -4189,7 +4189,8 @@
       </c>
       <c r="B244" s="1" t="inlineStr">
         <is>
-          <t>「Uah！ Rin-chan… fuu！ nngh, fuu！ chuchu！ chuu, chubuu！」</t>
+          <t>「Uah！ Rin-chan… fuu！ nngh, fuu！ chuchu！ chuu,
+chubuu！」</t>
         </is>
       </c>
       <c r="C244" t="n">
@@ -4513,8 +4514,8 @@
       </c>
       <c r="B265" s="1" t="inlineStr">
         <is>
-          <t>Rin-chan puffed her cheeks and made a gesture to cover
-her chest.</t>
+          <t>Rin-chan puffed her cheeks and made a gesture to
+cover her chest.</t>
         </is>
       </c>
       <c r="C265" t="n">
@@ -4667,8 +4668,8 @@
       </c>
       <c r="B275" s="1" t="inlineStr">
         <is>
-          <t>My feet take step after step, being drawn toward where
-Rin-chan is...</t>
+          <t>My feet take step after step, being drawn toward
+where Rin-chan is...</t>
         </is>
       </c>
       <c r="C275" t="n">
@@ -4714,8 +4715,8 @@
       </c>
       <c r="B278" s="1" t="inlineStr">
         <is>
-          <t>...Or so I think, but at this point she teases me even
-more.</t>
+          <t>...Or so I think, but at this point she teases me
+even more.</t>
         </is>
       </c>
       <c r="C278" t="n">
@@ -4868,8 +4869,8 @@
       </c>
       <c r="B288" s="1" t="inlineStr">
         <is>
-          <t>Because I granted Rin-chan's wish to see the fireworks
-too, things naturally ended up like this.</t>
+          <t>Because I granted Rin-chan's wish to see the
+fireworks too, things naturally ended up like this.</t>
         </is>
       </c>
       <c r="C288" t="n">
@@ -4944,8 +4945,8 @@
       </c>
       <c r="B293" s="1" t="inlineStr">
         <is>
-          <t>Rin-chan tells me in a dreamy tone that her between is
-all melting.</t>
+          <t>Rin-chan tells me in a dreamy tone that her between
+is all melting.</t>
         </is>
       </c>
       <c r="C293" t="n">
@@ -5235,8 +5236,8 @@
       </c>
       <c r="B312" s="1" t="inlineStr">
         <is>
-          <t>I said that, but holding Rin-chan means I'm distracted
-by her too.</t>
+          <t>I said that, but holding Rin-chan means I'm
+distracted by her too.</t>
         </is>
       </c>
       <c r="C312" t="n">
@@ -5723,8 +5724,9 @@
       </c>
       <c r="B344" s="1" t="inlineStr">
         <is>
-          <t>The feelings in her ear are surprisingly good, and she
-seems not to notice that she’s the one squeezing it.</t>
+          <t>The feelings in her ear are surprisingly good, and
+she seems not to notice that she’s the one squeezing
+it.</t>
         </is>
       </c>
       <c r="C344" t="n">
@@ -5875,8 +5877,8 @@
       </c>
       <c r="B354" s="1" t="inlineStr">
         <is>
-          <t>「Hawawa... ah！ Again, waaah！ This time it's so much...
-nmm！」</t>
+          <t>「Hawawa... ah！ Again, waaah！ This time it's so
+much... nmm！」</t>
         </is>
       </c>
       <c r="C354" t="n">
@@ -5983,7 +5985,8 @@
       </c>
       <c r="B361" s="1" t="inlineStr">
         <is>
-          <t>Then, as if lifting up her tiny body, I grind my hips.</t>
+          <t>Then, as if lifting up her tiny body, I grind my
+hips.</t>
         </is>
       </c>
       <c r="C361" t="n">
@@ -6443,7 +6446,8 @@
       </c>
       <c r="B391" s="1" t="inlineStr">
         <is>
-          <t>「I wonder... which spot makes Rin-chan feel the best?」</t>
+          <t>「I wonder... which spot makes Rin-chan feel the
+best?」</t>
         </is>
       </c>
       <c r="C391" t="n">
@@ -7532,8 +7536,8 @@
       </c>
       <c r="B462" s="1" t="inlineStr">
         <is>
-          <t>Before I knew it, Rin-chan had started moving her hips
-naturally.</t>
+          <t>Before I knew it, Rin-chan had started moving her
+hips naturally.</t>
         </is>
       </c>
       <c r="C462" t="n">
@@ -7824,7 +7828,8 @@
       <c r="B481" s="1" t="inlineStr">
         <is>
           <t>Excited from the kiss, Rin-chan's breathing grew
-ragged and uneven, and her body felt increasingly hot.</t>
+ragged and uneven, and her body felt increasingly
+hot.</t>
         </is>
       </c>
       <c r="C481" t="n">
@@ -7839,8 +7844,8 @@
       </c>
       <c r="B482" s="1" t="inlineStr">
         <is>
-          <t>…Then the little body went limp and sagged, its weight
-pressing down on my arm.</t>
+          <t>…Then the little body went limp and sagged, its
+weight pressing down on my arm.</t>
         </is>
       </c>
       <c r="C482" t="n">
@@ -8149,8 +8154,8 @@
       </c>
       <c r="B502" s="1" t="inlineStr">
         <is>
-          <t>Her skin is really starting to melt...—so much so that
-I could be mistaken.</t>
+          <t>Her skin is really starting to melt...—so much so
+that I could be mistaken.</t>
         </is>
       </c>
       <c r="C502" t="n">
@@ -8210,7 +8215,8 @@
       </c>
       <c r="B506" s="1" t="inlineStr">
         <is>
-          <t>「smack... lick！ sliiick... hah！ smack... ah！ smack...」</t>
+          <t>「smack... lick！ sliiick... hah！ smack... ah！
+smack...」</t>
         </is>
       </c>
       <c r="C506" t="n">
@@ -8332,8 +8338,8 @@
       </c>
       <c r="B514" s="1" t="inlineStr">
         <is>
-          <t>My attention had been down between my legs, so in that
-moment my mind froze.</t>
+          <t>My attention had been down between my legs, so in
+that moment my mind froze.</t>
         </is>
       </c>
       <c r="C514" t="n">
@@ -8424,8 +8430,8 @@
       </c>
       <c r="B520" s="1" t="inlineStr">
         <is>
-          <t>A surge of excitement rose all at once, and I returned
-her kisses like I was ravenous.</t>
+          <t>A surge of excitement rose all at once, and I
+returned her kisses like I was ravenous.</t>
         </is>
       </c>
       <c r="C520" t="n">
@@ -8623,8 +8629,8 @@
       </c>
       <c r="B533" s="1" t="inlineStr">
         <is>
-          <t>Her mouth below was soft and completely melted, so hot
-it felt like it could dissolve my penis.</t>
+          <t>Her mouth below was soft and completely melted, so
+hot it felt like it could dissolve my penis.</t>
         </is>
       </c>
       <c r="C533" t="n">
@@ -8762,8 +8768,8 @@
       </c>
       <c r="B542" s="1" t="inlineStr">
         <is>
-          <t>「Nn, un！ Aahh, it's amaaazing！ Rin — my body's... like
-it's not even mine！」</t>
+          <t>「Nn, un！ Aahh, it's amaaazing！ Rin — my body's...
+like it's not even mine！」</t>
         </is>
       </c>
       <c r="C542" t="n">
@@ -8778,7 +8784,8 @@
       </c>
       <c r="B543" s="1" t="inlineStr">
         <is>
-          <t>My hips won't stop, and I end up thrusting like crazy.</t>
+          <t>My hips won't stop, and I end up thrusting like
+crazy.</t>
         </is>
       </c>
       <c r="C543" t="n">
@@ -9036,8 +9043,8 @@
       </c>
       <c r="B560" s="1" t="inlineStr">
         <is>
-          <t>「Uwaaah, it's coming！ I'm cumming！ Rin-chan, make sure
-you swallow it... okay！？」</t>
+          <t>「Uwaaah, it's coming！ I'm cumming！ Rin-chan, make
+sure you swallow it... okay！？」</t>
         </is>
       </c>
       <c r="C560" t="n">
@@ -9651,8 +9658,8 @@
       </c>
       <c r="B600" s="1" t="inlineStr">
         <is>
-          <t>Rin-chan’s pussy trembles as I squeeze it, milking out
-every last drop.</t>
+          <t>Rin-chan’s pussy trembles as I squeeze it, milking
+out every last drop.</t>
         </is>
       </c>
       <c r="C600" t="n">
@@ -10034,8 +10041,8 @@
       </c>
       <c r="B625" s="1" t="inlineStr">
         <is>
-          <t>Even though the penis is still inside me, it's hard to
-say—I'm in a sort of dreamy bliss.</t>
+          <t>Even though the penis is still inside me, it's hard
+to say—I'm in a sort of dreamy bliss.</t>
         </is>
       </c>
       <c r="C625" t="n">

--- a/processed_ruby_restored_xlsx/sc234_凛６：花火.ss.xlsx
+++ b/processed_ruby_restored_xlsx/sc234_凛６：花火.ss.xlsx
@@ -885,7 +885,7 @@
       </c>
       <c r="B28" s="1" t="inlineStr">
         <is>
-          <t>「Can I say this？」</t>
+          <t>Can I say this？</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -915,7 +915,7 @@
       </c>
       <c r="B30" s="1" t="inlineStr">
         <is>
-          <t>「Hurry up, say it…！」</t>
+          <t>Hurry up, say it…！</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -1999,7 +1999,7 @@
       </c>
       <c r="B101" s="1" t="inlineStr">
         <is>
-          <t>「Ah... can I have one too？」</t>
+          <t>Ah... can I have one too？</t>
         </is>
       </c>
       <c r="C101" t="n">
@@ -2029,7 +2029,7 @@
       </c>
       <c r="B103" s="1" t="inlineStr">
         <is>
-          <t>「Ugh... okay, I guess I can't say no...」</t>
+          <t>Ugh... okay, I guess I can't say no...</t>
         </is>
       </c>
       <c r="C103" t="n">
@@ -2091,7 +2091,7 @@
       </c>
       <c r="B107" s="1" t="inlineStr">
         <is>
-          <t>「Nfu！ Okay, I'II dig in—！」</t>
+          <t>Nfu！ Okay, I'II dig in—！</t>
         </is>
       </c>
       <c r="C107" t="n">
@@ -2137,7 +2137,7 @@
       </c>
       <c r="B110" s="1" t="inlineStr">
         <is>
-          <t>「Amm... n, hamuu... n... nnn~...！」</t>
+          <t>Amm... n, hamuu... n... nnn~...！</t>
         </is>
       </c>
       <c r="C110" t="n">
@@ -2213,7 +2213,7 @@
       </c>
       <c r="B115" s="1" t="inlineStr">
         <is>
-          <t>「nnffuuuu！ hamu, hamu amuu... n~！」</t>
+          <t>nnffuuuu！ hamu, hamu amuu... n~！</t>
         </is>
       </c>
       <c r="C115" t="n">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="B117" s="1" t="inlineStr">
         <is>
-          <t>「hamu, nmunmu...」</t>
+          <t>hamu, nmunmu...</t>
         </is>
       </c>
       <c r="C117" t="n">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="B120" s="1" t="inlineStr">
         <is>
-          <t>「nffufu~！ amu, muuuu！ hyaa~！」</t>
+          <t>nffufu~！ amu, muuuu！ hyaa~！</t>
         </is>
       </c>
       <c r="C120" t="n">
@@ -2348,7 +2348,7 @@
       </c>
       <c r="B124" s="1" t="inlineStr">
         <is>
-          <t>「Heh, tasty？」</t>
+          <t>Heh, tasty？</t>
         </is>
       </c>
       <c r="C124" t="n">
@@ -3712,7 +3712,7 @@
       <c r="B213" s="1" t="inlineStr">
         <is>
           <t>As if just teasing my teeth wasn't enough anymore,
-her tongue started tangling with mine.</t>
+their tongue started tangling with mine.</t>
         </is>
       </c>
       <c r="C213" t="n">
@@ -4854,7 +4854,7 @@
       </c>
       <c r="B287" s="1" t="inlineStr">
         <is>
-          <t>In a station-box position, I insert my penis.</t>
+          <t>In a station-box position, he inserts his penis.</t>
         </is>
       </c>
       <c r="C287" t="n">
@@ -5940,7 +5940,7 @@
       </c>
       <c r="B358" s="1" t="inlineStr">
         <is>
-          <t>「Mmm！ I have to make your pussy feel so good...！」</t>
+          <t>Mmm！ I have to make your pussy feel so good...！</t>
         </is>
       </c>
       <c r="C358" t="n">
@@ -5985,7 +5985,7 @@
       </c>
       <c r="B361" s="1" t="inlineStr">
         <is>
-          <t>Then, as if lifting up her tiny body, I grind my
+          <t>Then, as if lifting up her tiny body, he grinds his
 hips.</t>
         </is>
       </c>
@@ -7338,7 +7338,7 @@
       <c r="B449" s="1" t="inlineStr">
         <is>
           <t>My sensitivity's through the roof, and even a kiss
-seems to do a lot, but I can't let her get away
+seems to do a lot, but I can't let them get away
 anymore...！</t>
         </is>
       </c>
@@ -8215,8 +8215,7 @@
       </c>
       <c r="B506" s="1" t="inlineStr">
         <is>
-          <t>「smack... lick！ sliiick... hah！ smack... ah！
-smack...」</t>
+          <t>smack... lick！ sliiick... hah！ smack... ah！ smack...</t>
         </is>
       </c>
       <c r="C506" t="n">
@@ -8246,7 +8245,7 @@
       </c>
       <c r="B508" s="1" t="inlineStr">
         <is>
-          <t>「Ah, nn~ uuh！ O-ochin！ Hii！ Nn-ah！」</t>
+          <t>Ah, nn~ uuh！ O-ochin！ Hii！ Nn-ah！</t>
         </is>
       </c>
       <c r="C508" t="n">
@@ -8768,8 +8767,8 @@
       </c>
       <c r="B542" s="1" t="inlineStr">
         <is>
-          <t>「Nn, un！ Aahh, it's amaaazing！ Rin — my body's...
-like it's not even mine！」</t>
+          <t>Nn, un！ Aahh, it's amaaazing！ Rin — my body's... like
+it's not even mine！</t>
         </is>
       </c>
       <c r="C542" t="n">
@@ -8846,7 +8845,8 @@
       </c>
       <c r="B547" s="1" t="inlineStr">
         <is>
-          <t>While working my hips, I just keep slobber-kissing.</t>
+          <t>While working his hips, he just keeps
+slobber-kissing.</t>
         </is>
       </c>
       <c r="C547" t="n">
@@ -8921,8 +8921,8 @@
       </c>
       <c r="B552" s="1" t="inlineStr">
         <is>
-          <t>「Hah, haa... Rin！ Like this... afun！ Okahikku, naa！
-Aa, uaa！」</t>
+          <t>Hah, haa... Rin！ Like this... afun！ Okahikku, naa！
+Aa, uaa！</t>
         </is>
       </c>
       <c r="C552" t="n">
@@ -9074,8 +9074,8 @@
       </c>
       <c r="B562" s="1" t="inlineStr">
         <is>
-          <t>「Fuaaah！ Rin-chan, do it properly... gulp it down...
-s-swipe it in！」</t>
+          <t>Fuaaah！ Rin-chan, do it properly... gulp it down...
+s-swipe it in！</t>
         </is>
       </c>
       <c r="C562" t="n">
@@ -9152,8 +9152,8 @@
       </c>
       <c r="B567" s="1" t="inlineStr">
         <is>
-          <t>「Fuwa! Ah! Ah! Niini! It's so hot... pyupyu's coming,
-uuu...!」</t>
+          <t>Fuwa! Ah! Ah! Niini! It's so hot... pyupyu's coming,
+uuu...!</t>
         </is>
       </c>
       <c r="C567" t="n">
@@ -9183,8 +9183,8 @@
       </c>
       <c r="B569" s="1" t="inlineStr">
         <is>
-          <t>「Waaah！  Hah, haaah！  Aaaah！  It's coming out... ugh,
-hah！」</t>
+          <t>Waaah！  Hah, haaah！  Aaaah！  It's coming out... ugh,
+hah！</t>
         </is>
       </c>
       <c r="C569" t="n">
@@ -9199,8 +9199,8 @@
       </c>
       <c r="B570" s="1" t="inlineStr">
         <is>
-          <t>My penis pulsing and throbbing, I jet out a plentiful
-stream of semen.</t>
+          <t>His penis pulsing and throbbing, he jets out a
+plentiful stream of semen.</t>
         </is>
       </c>
       <c r="C570" t="n">
@@ -9275,7 +9275,7 @@
       </c>
       <c r="B575" s="1" t="inlineStr">
         <is>
-          <t>「Uah！ Hah, hah！ Rin-chan！ Hah, fuuu, fuha！」</t>
+          <t>Uah！ Hah, hah！ Rin-chan！ Hah, fuuu, fuha！</t>
         </is>
       </c>
       <c r="C575" t="n">
@@ -9305,8 +9305,8 @@
       </c>
       <c r="B577" s="1" t="inlineStr">
         <is>
-          <t>「Uuu~ nyaah！ Niini's... sei, ekkii... oihi！ Oihii...
-tte, itte uu！」</t>
+          <t>Uuu~ nyaah！ Niini's... sei, ekkii... oihi！ Oihii...
+tte, itte uu！</t>
         </is>
       </c>
       <c r="C577" t="n">
@@ -9336,8 +9336,8 @@
       </c>
       <c r="B579" s="1" t="inlineStr">
         <is>
-          <t>It’s like she’s saying she wants more semen so badly
-she can’t stand it.</t>
+          <t>It’s like they’re saying they want more semen so
+badly they can’t stand it.</t>
         </is>
       </c>
       <c r="C579" t="n">
@@ -9475,8 +9475,8 @@
       </c>
       <c r="B588" s="1" t="inlineStr">
         <is>
-          <t>Even though my penis was still feeling good, I just
-let that pleasure wash over me.</t>
+          <t>Even though his penis was still feeling good, he just
+let that pleasure wash over him.</t>
         </is>
       </c>
       <c r="C588" t="n">
@@ -9551,7 +9551,7 @@
       </c>
       <c r="B593" s="1" t="inlineStr">
         <is>
-          <t>「Nnheah... Aahh！ Wait—kyuruu！ I'm cominggg！」</t>
+          <t>Nnheah... Aahh！ Wait—kyuruu！ I'm cominggg！</t>
         </is>
       </c>
       <c r="C593" t="n">
@@ -9658,7 +9658,7 @@
       </c>
       <c r="B600" s="1" t="inlineStr">
         <is>
-          <t>Rin-chan’s pussy trembles as I squeeze it, milking
+          <t>Rin-chan’s pussy trembles as he squeezes it, milking
 out every last drop.</t>
         </is>
       </c>
@@ -9705,7 +9705,7 @@
       </c>
       <c r="B603" s="1" t="inlineStr">
         <is>
-          <t>「Huff... huff...puh」</t>
+          <t>Huff... huff...puh</t>
         </is>
       </c>
       <c r="C603" t="n">
@@ -9735,7 +9735,7 @@
       </c>
       <c r="B605" s="1" t="inlineStr">
         <is>
-          <t>「Muu... ho, hoh？ My body's not moving...」</t>
+          <t>Muu... ho, hoh？ My body's not moving...</t>
         </is>
       </c>
       <c r="C605" t="n">
